--- a/example_data/modelspec.xlsx
+++ b/example_data/modelspec.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="2" activeTab="2"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="56">
   <si>
     <t xml:space="preserve">objectclass</t>
   </si>
@@ -164,34 +164,34 @@
     <t xml:space="preserve">2021-01-09T00:00:00</t>
   </si>
   <si>
+    <t xml:space="preserve">parameter name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">alternative name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parameter value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">resolution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 Y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">db_mip_solver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HiGHS.jl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">db_lp_solver</t>
+  </si>
+  <si>
     <t xml:space="preserve">l</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parameter name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">alternative name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parameter value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">resolution</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 h</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 Y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">db_mip_solver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HiGHS.jl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">db_lp_solver</t>
   </si>
 </sst>
 </file>
@@ -280,7 +280,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -296,10 +296,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="false" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
@@ -964,12 +960,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="1" style="4" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="5" width="17.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="5" width="18.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="4" width="17.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="4" width="18.42"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1002,7 +998,7 @@
       <c r="D2" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="5" t="s">
         <v>43</v>
       </c>
     </row>
@@ -1019,17 +1015,11 @@
       <c r="D3" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="5" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C21" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
   </sheetData>
-  <sheetProtection sheet="true" objects="true" scenarios="true"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1048,11 +1038,11 @@
   <dimension ref="A1:E3"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="5" width="19.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="5" width="18.97"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="5" width="19.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="5" width="15.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="5" width="15.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="4" width="19.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="4" width="18.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="4" width="19.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="4" width="15.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="4" width="15.08"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1063,13 +1053,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1080,13 +1070,13 @@
         <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>51</v>
+      <c r="E2" s="4" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1097,13 +1087,13 @@
         <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>52</v>
+      <c r="E3" s="4" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1139,13 +1129,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1156,13 +1146,13 @@
         <v>3</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>42</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1173,24 +1163,24 @@
         <v>3</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>42</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G4" s="7"/>
+      <c r="G4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G5" s="7"/>
+      <c r="G5" s="6"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C21" s="1" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
